--- a/test-cases/OnlineEdu_功能测试用例.xlsx
+++ b/test-cases/OnlineEdu_功能测试用例.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkBuddy\OnlineEdu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkBuddy\EduWise-functional-test\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4DB59B-4D55-42E9-B2E3-1A68FB64378F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AA617E-B1A9-4171-9B49-FAE8778D048B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="824" firstSheet="5" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5830" yWindow="1340" windowWidth="17260" windowHeight="12850" tabRatio="824" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="汇总统计" sheetId="1" r:id="rId1"/>
@@ -3916,7 +3916,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3979,10 +3979,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4348,8 +4345,8 @@
       <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="27">
-        <v>0</v>
+      <c r="H2" s="26">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -4374,7 +4371,7 @@
       <c r="G3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="27">
+      <c r="H3" s="26">
         <v>0</v>
       </c>
     </row>
@@ -4400,7 +4397,7 @@
       <c r="G4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="26">
         <v>1</v>
       </c>
     </row>
@@ -4426,7 +4423,7 @@
       <c r="G5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="26">
         <v>0</v>
       </c>
     </row>
@@ -4452,7 +4449,7 @@
       <c r="G6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="26">
         <v>2</v>
       </c>
     </row>
@@ -4478,7 +4475,7 @@
       <c r="G7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="26">
         <v>1</v>
       </c>
     </row>
@@ -4504,7 +4501,7 @@
       <c r="G8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="26">
         <v>0</v>
       </c>
     </row>
@@ -4530,7 +4527,7 @@
       <c r="G9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="26">
         <v>0</v>
       </c>
     </row>
@@ -4556,7 +4553,7 @@
       <c r="G10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="26">
         <v>1</v>
       </c>
     </row>
@@ -4582,7 +4579,7 @@
       <c r="G11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="26">
         <v>1</v>
       </c>
     </row>
@@ -4608,7 +4605,7 @@
       <c r="G12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="26">
         <v>1</v>
       </c>
     </row>
@@ -4634,8 +4631,8 @@
       <c r="G13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H13" s="27">
-        <v>1</v>
+      <c r="H13" s="26">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -4660,7 +4657,7 @@
       <c r="G14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="26">
         <v>1</v>
       </c>
     </row>
@@ -4686,7 +4683,7 @@
       <c r="G15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="26">
         <v>0</v>
       </c>
     </row>
@@ -4712,7 +4709,7 @@
       <c r="G16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="26">
         <v>0</v>
       </c>
     </row>
@@ -4738,7 +4735,7 @@
       <c r="G17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="26">
         <v>0</v>
       </c>
     </row>
@@ -4764,7 +4761,7 @@
         <v>10</v>
       </c>
       <c r="G18" s="4"/>
-      <c r="H18" s="28">
+      <c r="H18" s="27">
         <f>SUM(H2:H17)</f>
         <v>9</v>
       </c>
@@ -5879,10 +5876,10 @@
         <v>795</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>490</v>
+        <v>464</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6081,19 +6078,19 @@
       <c r="J10" s="15"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J11" s="26"/>
+      <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J12" s="26"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J13" s="26"/>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J14" s="26"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J15" s="26"/>
+      <c r="J15" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -9884,19 +9881,19 @@
       <c r="J12" s="15"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J13" s="26"/>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J14" s="26"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J15" s="26"/>
+      <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J16" s="26"/>
+      <c r="J16" s="16"/>
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J17" s="26"/>
+      <c r="J17" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
